--- a/werkomgeving/Mapping CIM met LGM.xlsx
+++ b/werkomgeving/Mapping CIM met LGM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\github.com\mim-metamodel\werkomgeving\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD17350D-9966-455B-B548-1805AA5819CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A5C41D-4F73-4539-B367-4D17F8F3D7CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-5610" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{DB64FF7E-3480-49F2-99C2-692AB8F2E1C2}"/>
   </bookViews>
@@ -585,7 +585,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> = niet meer opgenomen in de huidige versie vanhet begrippenkader</t>
+      <t xml:space="preserve"> = niet meer opgenomen in de huidige versie van het begrippenkader.</t>
     </r>
   </si>
 </sst>
@@ -3846,10 +3846,10 @@
       <c r="C63" s="122" t="s">
         <v>149</v>
       </c>
-      <c r="D63" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="E63" s="15" t="s">
+      <c r="D63" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="E63" s="28" t="s">
         <v>111</v>
       </c>
       <c r="F63" s="41"/>
@@ -3902,10 +3902,10 @@
       <c r="C66" s="122" t="s">
         <v>149</v>
       </c>
-      <c r="D66" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="E66" s="15" t="s">
+      <c r="D66" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="E66" s="28" t="s">
         <v>111</v>
       </c>
       <c r="F66" s="41"/>
@@ -3960,10 +3960,10 @@
       <c r="C69" s="122" t="s">
         <v>149</v>
       </c>
-      <c r="D69" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="E69" s="15" t="s">
+      <c r="D69" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="E69" s="28" t="s">
         <v>111</v>
       </c>
       <c r="F69" s="41"/>
